--- a/AAII_Financials/Quarterly/HIG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HIG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>HIG</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7224000</v>
+        <v>7261000</v>
       </c>
       <c r="E8" s="3">
+        <v>6939000</v>
+      </c>
+      <c r="F8" s="3">
         <v>7348000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7232000</v>
       </c>
-      <c r="G8" s="3">
-        <v>6987000</v>
-      </c>
       <c r="H8" s="3">
-        <v>6809000</v>
+        <v>6716000</v>
       </c>
       <c r="I8" s="3">
+        <v>6545000</v>
+      </c>
+      <c r="J8" s="3">
         <v>6889000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6757000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6491000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6423000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6413000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6171000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6053000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5916000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6016000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5580000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5373000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5393000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5816000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5686000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5589000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5299000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5328000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5171000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5068000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4956000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5362000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5348000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5092000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4944000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4634000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4846000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4789000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4693000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4591000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4196000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4218000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4172000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>16142000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4730000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4750000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4654000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4378000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4432000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4337000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4607000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4370000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4408000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4222000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4156000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4167000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4060000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4082000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3973000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>475000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>467000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>453000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>440000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>428000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>419000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>417000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>416000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>419000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>421000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>429000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>437000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>438000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>437000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>392000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>355000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>350000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>348000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>344000</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>342000</v>
       </c>
       <c r="AK9" s="3">
         <v>342000</v>
       </c>
       <c r="AL9" s="3">
+        <v>342000</v>
+      </c>
+      <c r="AM9" s="3">
         <v>341000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>345000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>344000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1377000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>403000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2570000</v>
+        <v>2511000</v>
       </c>
       <c r="E10" s="3">
+        <v>2285000</v>
+      </c>
+      <c r="F10" s="3">
         <v>2970000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2800000</v>
       </c>
-      <c r="G10" s="3">
-        <v>2650000</v>
-      </c>
       <c r="H10" s="3">
-        <v>2202000</v>
+        <v>2379000</v>
       </c>
       <c r="I10" s="3">
+        <v>1938000</v>
+      </c>
+      <c r="J10" s="3">
         <v>2519000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2349000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2269000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2267000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2246000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2111000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1971000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1943000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5541000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5113000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4920000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4953000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5388000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5267000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5172000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4883000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4909000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4750000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4639000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4519000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4924000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4911000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4700000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4589000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4284000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4498000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4445000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4351000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4249000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3855000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3873000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3828000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>14765000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>4327000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,8 +1244,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1353,8 +1367,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,8 +1492,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,92 +1515,92 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>3000</v>
       </c>
       <c r="S14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T14" s="3">
         <v>11000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-12000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>17000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>87000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>91000</v>
       </c>
       <c r="AE14" s="3">
         <v>91000</v>
       </c>
       <c r="AF14" s="3">
+        <v>91000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>4000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2000</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>4000</v>
       </c>
       <c r="AL14" s="3">
         <v>4000</v>
@@ -1589,21 +1609,24 @@
         <v>4000</v>
       </c>
       <c r="AN14" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AO14" s="3">
         <v>3000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>685000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="E15" s="3">
         <v>18000</v>
@@ -1612,10 +1635,10 @@
         <v>18000</v>
       </c>
       <c r="G15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="H15" s="3">
         <v>17000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>18000</v>
       </c>
       <c r="I15" s="3">
         <v>18000</v>
@@ -1624,10 +1647,10 @@
         <v>18000</v>
       </c>
       <c r="K15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="L15" s="3">
         <v>17000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>18000</v>
       </c>
       <c r="M15" s="3">
         <v>18000</v>
@@ -1636,10 +1659,10 @@
         <v>18000</v>
       </c>
       <c r="O15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="P15" s="3">
         <v>17000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>18000</v>
       </c>
       <c r="Q15" s="3">
         <v>18000</v>
@@ -1648,10 +1671,10 @@
         <v>18000</v>
       </c>
       <c r="S15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="T15" s="3">
         <v>17000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>18000</v>
       </c>
       <c r="U15" s="3">
         <v>18000</v>
@@ -1660,22 +1683,22 @@
         <v>18000</v>
       </c>
       <c r="W15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="X15" s="3">
         <v>17000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>18000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>17000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>18000</v>
       </c>
       <c r="AA15" s="3">
         <v>18000</v>
       </c>
       <c r="AB15" s="3">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="AC15" s="3">
         <v>19000</v>
@@ -1684,16 +1707,16 @@
         <v>19000</v>
       </c>
       <c r="AE15" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>15000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>13000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>14000</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>18000</v>
       </c>
       <c r="AI15" s="3">
         <v>18000</v>
@@ -1702,25 +1725,28 @@
         <v>18000</v>
       </c>
       <c r="AK15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AL15" s="3">
         <v>11000</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>1000</v>
       </c>
       <c r="AM15" s="3">
         <v>1000</v>
       </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AN15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AO15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>4000</v>
       </c>
-      <c r="AP15" s="3" t="s">
+      <c r="AQ15" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6119000</v>
+        <v>5982000</v>
       </c>
       <c r="E17" s="3">
+        <v>5900000</v>
+      </c>
+      <c r="F17" s="3">
         <v>5877000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5864000</v>
       </c>
-      <c r="G17" s="3">
-        <v>5691000</v>
-      </c>
       <c r="H17" s="3">
-        <v>5977000</v>
+        <v>5492000</v>
       </c>
       <c r="I17" s="3">
+        <v>5772000</v>
+      </c>
+      <c r="J17" s="3">
         <v>5755000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5749000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5524000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5457000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5399000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5304000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5324000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5207000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5234000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5099000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4770000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4788000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4854000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5045000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4422000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4939000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4619000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4581000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4419000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4548000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4621000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4628000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4573000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4105000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4397000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4247000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4173000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4094000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4091000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3936000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4420000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3691000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>15368000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4116000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1105000</v>
+        <v>1279000</v>
       </c>
       <c r="E18" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1471000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1368000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1296000</v>
-      </c>
       <c r="H18" s="3">
-        <v>832000</v>
+        <v>1224000</v>
       </c>
       <c r="I18" s="3">
+        <v>773000</v>
+      </c>
+      <c r="J18" s="3">
         <v>1134000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1008000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>967000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>966000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1014000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>867000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>729000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>709000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>782000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>481000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>603000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>605000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>962000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>641000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1167000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>360000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>709000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>590000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>649000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>408000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>741000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>720000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>519000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>839000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>237000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>599000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>616000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>599000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>500000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>260000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-202000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>481000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>774000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>614000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,31 +2081,32 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-3000</v>
       </c>
       <c r="K20" s="3">
         <v>-3000</v>
@@ -2081,20 +2115,20 @@
         <v>-3000</v>
       </c>
       <c r="M20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N20" s="3">
         <v>7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2170,192 +2204,198 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1126000</v>
+        <v>1298000</v>
       </c>
       <c r="E21" s="3">
+        <v>1060000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1481000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1389000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1315000</v>
-      </c>
       <c r="H21" s="3">
-        <v>853000</v>
+        <v>1243000</v>
       </c>
       <c r="I21" s="3">
+        <v>794000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1143000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1029000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>987000</v>
       </c>
       <c r="L21" s="3">
         <v>987000</v>
       </c>
       <c r="M21" s="3">
+        <v>987000</v>
+      </c>
+      <c r="N21" s="3">
         <v>1025000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>887000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>749000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>729000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1397000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1101000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1220000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1213000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1555000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1228000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1757000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>950000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1279000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1153000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1213000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>979000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1297000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1269000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1302000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>695000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1069000</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>1098000</v>
       </c>
       <c r="AJ21" s="3">
         <v>1098000</v>
       </c>
       <c r="AK21" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="AL21" s="3">
         <v>928000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>726000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>261000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>940000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2695000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1129000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E22" s="3">
         <v>51000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>50000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>53000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>52000</v>
       </c>
       <c r="H22" s="3">
         <v>52000</v>
       </c>
       <c r="I22" s="3">
+        <v>52000</v>
+      </c>
+      <c r="J22" s="3">
         <v>51000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>58000</v>
       </c>
       <c r="K22" s="3">
         <v>58000</v>
       </c>
       <c r="L22" s="3">
+        <v>58000</v>
+      </c>
+      <c r="M22" s="3">
         <v>57000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>55000</v>
       </c>
       <c r="N22" s="3">
         <v>55000</v>
       </c>
       <c r="O22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="P22" s="3">
         <v>57000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>58000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>50000</v>
       </c>
       <c r="R22" s="3">
         <v>50000</v>
       </c>
       <c r="S22" s="3">
+        <v>50000</v>
+      </c>
+      <c r="T22" s="3">
         <v>51000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>62000</v>
       </c>
       <c r="U22" s="3">
         <v>62000</v>
       </c>
       <c r="V22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="W22" s="3">
         <v>58000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>57000</v>
       </c>
       <c r="X22" s="3">
         <v>57000</v>
@@ -2364,302 +2404,311 @@
         <v>57000</v>
       </c>
       <c r="Z22" s="3">
+        <v>57000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>58000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>57000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>64000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>65000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>67000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>63000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>64000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>70000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>69000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>80000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>78000</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>79000</v>
       </c>
       <c r="AM22" s="3">
         <v>79000</v>
       </c>
       <c r="AN22" s="3">
+        <v>79000</v>
+      </c>
+      <c r="AO22" s="3">
         <v>80000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>327000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1057000</v>
+        <v>1231000</v>
       </c>
       <c r="E23" s="3">
+        <v>991000</v>
+      </c>
+      <c r="F23" s="3">
         <v>1413000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1318000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1246000</v>
-      </c>
       <c r="H23" s="3">
-        <v>783000</v>
+        <v>1174000</v>
       </c>
       <c r="I23" s="3">
+        <v>724000</v>
+      </c>
+      <c r="J23" s="3">
         <v>1074000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>952000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>912000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>911000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>950000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>813000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>672000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>653000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>732000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>431000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>552000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>543000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>900000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>583000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1110000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>303000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>652000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>532000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>592000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>344000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>676000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>653000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>456000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>775000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>167000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>530000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>537000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>519000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>422000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>181000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-281000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>401000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>447000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>528000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>201000</v>
+        <v>251000</v>
       </c>
       <c r="E24" s="3">
+        <v>187000</v>
+      </c>
+      <c r="F24" s="3">
         <v>282000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>238000</v>
       </c>
-      <c r="G24" s="3">
-        <v>251000</v>
-      </c>
       <c r="H24" s="3">
-        <v>153000</v>
+        <v>236000</v>
       </c>
       <c r="I24" s="3">
+        <v>140000</v>
+      </c>
+      <c r="J24" s="3">
         <v>221000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>185000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>174000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>158000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>179000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>162000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>125000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>118000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>143000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>92000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>110000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>98000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>171000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>101000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>205000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>54000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>121000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>73000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>124000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>71000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>128000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>118000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>84000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>145000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7000</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>103000</v>
       </c>
       <c r="AI24" s="3">
         <v>103000</v>
       </c>
       <c r="AJ24" s="3">
+        <v>103000</v>
+      </c>
+      <c r="AK24" s="3">
         <v>94000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>103000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>36000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-129000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>98000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-166000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>856000</v>
+        <v>980000</v>
       </c>
       <c r="E26" s="3">
+        <v>804000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1131000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1080000</v>
       </c>
-      <c r="G26" s="3">
-        <v>995000</v>
-      </c>
       <c r="H26" s="3">
+        <v>938000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>584000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>853000</v>
+      </c>
+      <c r="K26" s="3">
+        <v>767000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>738000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>753000</v>
+      </c>
+      <c r="N26" s="3">
+        <v>771000</v>
+      </c>
+      <c r="O26" s="3">
+        <v>651000</v>
+      </c>
+      <c r="P26" s="3">
+        <v>547000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>535000</v>
+      </c>
+      <c r="R26" s="3">
+        <v>589000</v>
+      </c>
+      <c r="S26" s="3">
+        <v>339000</v>
+      </c>
+      <c r="T26" s="3">
+        <v>442000</v>
+      </c>
+      <c r="U26" s="3">
+        <v>445000</v>
+      </c>
+      <c r="V26" s="3">
+        <v>729000</v>
+      </c>
+      <c r="W26" s="3">
+        <v>482000</v>
+      </c>
+      <c r="X26" s="3">
+        <v>905000</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>249000</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>531000</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>459000</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>468000</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>273000</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>548000</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>535000</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>372000</v>
+      </c>
+      <c r="AG26" s="3">
         <v>630000</v>
       </c>
-      <c r="I26" s="3">
-        <v>853000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>767000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>738000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>753000</v>
-      </c>
-      <c r="M26" s="3">
-        <v>771000</v>
-      </c>
-      <c r="N26" s="3">
-        <v>651000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>547000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>535000</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>589000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>339000</v>
-      </c>
-      <c r="S26" s="3">
-        <v>442000</v>
-      </c>
-      <c r="T26" s="3">
-        <v>445000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>729000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>482000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>905000</v>
-      </c>
-      <c r="X26" s="3">
-        <v>249000</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>531000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>459000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>468000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>273000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>548000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>535000</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>372000</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>630000</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>160000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>427000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>434000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>425000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>319000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>145000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-152000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>303000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>613000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>438000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1293000</v>
+      </c>
+      <c r="E27" s="3">
         <v>851000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1126000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1074000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>990000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>625000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>848000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>761000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>733000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>748000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>766000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>645000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>542000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>530000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>584000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>333000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>437000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>440000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>724000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>476000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>900000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>244000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>526000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>453000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>463000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>268000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>543000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>524000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>372000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>625000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>154000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>427000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>434000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>425000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>319000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>145000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-152000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>303000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>613000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>438000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,16 +3204,19 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>318000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -3164,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -3196,8 +3257,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -3214,11 +3275,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>6000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3226,8 +3287,8 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3239,37 +3300,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>36000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>5000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>148000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>172000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-4022000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>89000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>112000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>75000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>283000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,31 +3579,34 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3000</v>
       </c>
       <c r="K32" s="3">
         <v>3000</v>
@@ -3545,20 +3615,20 @@
         <v>3000</v>
       </c>
       <c r="M32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N32" s="3">
         <v>-7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3634,130 +3704,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="E33" s="3">
         <v>856000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1131000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1080000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>995000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>630000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>853000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>767000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>738000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>753000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>771000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>651000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>547000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>535000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>584000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>333000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>437000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>440000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>724000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>476000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>900000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>244000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>532000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>453000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>463000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>268000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>543000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>524000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>372000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>625000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>190000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>432000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>582000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>597000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3703000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>234000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-40000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>378000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>896000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>438000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="E35" s="3">
         <v>856000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1131000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1080000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>995000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>630000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>853000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>767000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>738000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>753000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>771000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>651000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>547000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>535000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>584000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>333000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>437000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>440000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>724000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>476000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>900000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>244000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>532000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>453000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>463000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>268000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>543000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>524000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>372000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>625000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>190000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>432000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>582000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>597000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3703000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>234000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-40000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>378000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>896000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>438000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,175 +4301,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E41" s="3">
         <v>166000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>133000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>150000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>166000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>138000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>183000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>223000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>154000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>274000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>150000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>152000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>229000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>175000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>258000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>223000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>205000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>232000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>177000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>176000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>151000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>173000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>291000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>211000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>185000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>207000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>226000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>104000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>121000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>102000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>147000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>228000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>180000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>333000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>362000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>337000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>328000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>810000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3866000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4228000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4353000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4220000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3649000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3366000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4068000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3965000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3701000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2976000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3850000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3304000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3237000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4063000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4459,130 +4549,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7009000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6729000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6391000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6555000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6698000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6386000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6010000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6151000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6335000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5988000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5607000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5535000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5578000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5271000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4949000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4990000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4996000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4787000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4445000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4598000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4622000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4487000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4268000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4450000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4595000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4558000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4384000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4580000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4726000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4160000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3995000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4025000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4001000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3994000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3910000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3846000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3764000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3730000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4625,8 +4721,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4703,53 +4799,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8422000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7685000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7592000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7682000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7647000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7527000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7913000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7936000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7507000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7302000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7282000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7396000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4825,53 +4924,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19500000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18777000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18606000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18573000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18166000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17650000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17959000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17924000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18159000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17222000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17153000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16322000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16319000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16948000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4947,359 +5049,368 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52093000</v>
+      </c>
+      <c r="E47" s="3">
         <v>51685000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>52080000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>51034000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>50080000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49776000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>48019000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48264000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46076000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46380000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45287000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>43298000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>42692000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42963000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>52560000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50661000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>52392000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55951000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>57749000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>57574000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>56787000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>55727000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>56532000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>54778000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>53028000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>50359000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>53030000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>52577000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>50769000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>47895000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>46790000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>46134000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45648000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>44432000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>45146000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>72993000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>73780000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>72189000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>41201000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>73719000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E48" s="3">
         <v>923000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>931000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>925000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>906000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>909000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>888000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>871000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>878000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>879000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>896000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>894000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>884000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>904000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>927000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>941000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>970000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>995000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1027000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1047000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1067000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1092000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1122000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1144000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1135000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1161000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1181000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1194000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1222000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1145000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>997000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1013000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1018000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1034000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>962000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>974000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>984000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>991000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3624000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3854000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3824000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3874000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3875000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3817000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3787000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3835000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3828000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3770000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3731000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3760000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3750000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3726000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2689000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2707000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2724000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2746000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2769000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2792000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2815000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2838000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2861000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2884000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2907000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2941000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2983000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3039000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3104000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1934000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1947000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1941000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1959000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1977000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1949000</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>567000</v>
       </c>
       <c r="AM49" s="3">
         <v>567000</v>
@@ -5308,13 +5419,16 @@
         <v>567000</v>
       </c>
       <c r="AO49" s="3">
+        <v>567000</v>
+      </c>
+      <c r="AP49" s="3">
         <v>611000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>567000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3430000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3146000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2818000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3104000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3055000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2701000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2639000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2934000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2514000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2080000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2453000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2740000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2888000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2401000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1552000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1617000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1281000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>789000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>402000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>541000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>462000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>474000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>311000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>313000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>211000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>592000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>376000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>459000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>672000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>921000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1248000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1244000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1282000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>157766000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>166100000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2766000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2868000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4028000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>172019000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>3360000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87983000</v>
+      </c>
+      <c r="E54" s="3">
         <v>86322000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85997000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84995000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>83639000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>82307000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>80917000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>81219000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79046000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77710000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76780000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74516000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>73895000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>74249000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>73008000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>71801000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>72402000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>75252000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>76578000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>76290000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>74732000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>74201000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>74111000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>72319000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70990000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>68724000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70817000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70256000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>69472000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>63324000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>62307000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>61437000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>60775000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>216666000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>225260000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>224211000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>225863000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>225388000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>224576000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>228430000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,8 +6141,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6055,8 +6186,8 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6133,64 +6264,67 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>40000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>6000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>3000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>591000</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -6201,8 +6335,8 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -6214,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>500000</v>
@@ -6223,10 +6357,10 @@
         <v>500000</v>
       </c>
       <c r="AF58" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AG58" s="3">
         <v>499000</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>413000</v>
       </c>
       <c r="AH58" s="3">
         <v>413000</v>
@@ -6238,7 +6372,7 @@
         <v>413000</v>
       </c>
       <c r="AK58" s="3">
-        <v>320000</v>
+        <v>413000</v>
       </c>
       <c r="AL58" s="3">
         <v>320000</v>
@@ -6250,180 +6384,186 @@
         <v>320000</v>
       </c>
       <c r="AO58" s="3">
+        <v>320000</v>
+      </c>
+      <c r="AP58" s="3">
         <v>416000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10996000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10477000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10070000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10403000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10379000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9877000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9420000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9612000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9490000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9001000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8631000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8713000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8672000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8278000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9111000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9160000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9078000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8809000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8661000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8555000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8463000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8280000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7968000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8122000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8274000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8197000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8226000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8438000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8493000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7039000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6691000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6819000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6898000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6928000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6851000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>165552000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>166941000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>167105000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>121981000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>197367000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11006000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10478000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10110000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10405000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10380000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9879000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9420000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9618000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9491000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8998000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8625000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8713000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8675000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8278000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6499,175 +6639,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4374000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4372000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4503000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4370000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4369000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4368000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4511000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4365000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4364000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4363000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4506000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4361000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4360000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4358000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4357000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4356000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4355000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4354000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4944000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4943000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4354000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4353000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4352000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4351000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4350000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4349000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4348000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4346000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4050000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3767000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4265000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4263000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4262000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4755000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4678000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4818000</v>
-      </c>
-      <c r="AM61" s="3">
-        <v>4817000</v>
       </c>
       <c r="AN61" s="3">
         <v>4817000</v>
       </c>
       <c r="AO61" s="3">
+        <v>4817000</v>
+      </c>
+      <c r="AP61" s="3">
         <v>4494000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4635000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52156000</v>
+      </c>
+      <c r="E62" s="3">
         <v>51769000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>51135000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>51770000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>50514000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>51184000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>49143000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>50106000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>49363000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48696000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46673000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47169000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46114000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47273000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6681,22 +6827,22 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>151000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>164000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>148000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>158000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>153000</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
@@ -6713,8 +6859,8 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -6723,28 +6869,31 @@
         <v>0</v>
       </c>
       <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
         <v>154194000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>162442000</v>
       </c>
-      <c r="AL62" s="3">
-        <v>0</v>
-      </c>
       <c r="AM62" s="3">
         <v>0</v>
       </c>
       <c r="AN62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3">
         <v>661000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>163534000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68350000</v>
+      </c>
+      <c r="E66" s="3">
         <v>67433000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67018000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66545000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66121000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65463000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>64470000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64211000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63366000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62242000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61453000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>60837000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59743000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59909000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59332000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>58846000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58176000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59355000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>58735000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>58428000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56488000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>56499000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>55555000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>54517000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>53918000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>53458000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54547000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>54178000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>54180000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>48984000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49206000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>48708000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>48229000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>203523000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>211766000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>206978000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>208575000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>208379000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>207673000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>209772000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7615,7 +7783,7 @@
         <v>334000</v>
       </c>
       <c r="AH70" s="3">
-        <v>0</v>
+        <v>334000</v>
       </c>
       <c r="AI70" s="3">
         <v>0</v>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26553000</v>
+      </c>
+      <c r="E72" s="3">
         <v>25424000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24739000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23779000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22850000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22007000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21531000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20834000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20209000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19614000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19007000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18382000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17865000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17454000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17058000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16598000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16388000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16077000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15764000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15169000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14813000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14036000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13918000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13503000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13167000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12819000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12685000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12251000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11836000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11572000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11055000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10973000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10649000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10156000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9642000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13434000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13282000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13406000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13114000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>13282000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19299000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18555000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18645000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18116000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17184000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16510000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16113000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16674000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15346000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15134000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14993000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13345000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13818000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14006000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13342000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12621000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13892000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15563000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17509000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17528000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17910000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17368000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18222000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17468000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16738000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14932000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15936000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15744000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14958000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14006000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12767000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12729000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12546000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13143000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13494000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17233000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>17288000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>17009000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>16903000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>18658000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="E81" s="3">
         <v>856000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1131000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1080000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>995000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>630000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>853000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>767000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>738000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>753000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>771000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>651000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>547000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>535000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>584000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>333000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>437000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>440000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>724000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>476000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>900000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>244000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>532000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>453000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>463000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>268000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>543000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>524000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>372000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>625000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>190000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>432000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>582000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>597000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3703000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>234000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-40000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>378000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>896000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>438000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E83" s="3">
         <v>74000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-24000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>67000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>43000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>109000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>110000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>112000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>111000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>35000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>138000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>150000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>153000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>615000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>620000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>617000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>608000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>593000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>587000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>590000</v>
       </c>
       <c r="X83" s="3">
         <v>590000</v>
       </c>
       <c r="Y83" s="3">
+        <v>590000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>570000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>563000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>564000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>571000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>556000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>549000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>505000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>463000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>458000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>470000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>482000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>499000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>428000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>466000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>463000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>459000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1921000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>515000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1045000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1808000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1838000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1291000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>985000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1874000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1678000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1260000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1097000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1627000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1771000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-49000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>871000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1084000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1521000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>974000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>429000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1277000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1294000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>820000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>760000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1216000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1330000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>969000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>298000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1043000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1442000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>725000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>279000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1001000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>572000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>835000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>972000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>364000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>652000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>644000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>543000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2066000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>26000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-61000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-64000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-52000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-50000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-53000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-45000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-31000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-41000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-121000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-37000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-51000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-551000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-332000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1299000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-743000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-401000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1356000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1089000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-888000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-435000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1165000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1319000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>499000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-446000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-572000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1092000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>261000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>126000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-718000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1169000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-129000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-450000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1059000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-562000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>777000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-828000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1350000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-99000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>129000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1200000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-555000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>43000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-268000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1208000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>949000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>604000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,103 +10451,104 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E96" s="3">
         <v>167000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>146000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>147000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>149000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>150000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>137000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>138000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>140000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>141000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>129000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>131000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>134000</v>
       </c>
       <c r="P96" s="3">
         <v>134000</v>
       </c>
       <c r="Q96" s="3">
+        <v>134000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-123000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-126000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-127000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-130000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-120000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-123000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-126000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-116000</v>
       </c>
       <c r="Y96" s="3">
         <v>-116000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-117000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-116000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-108000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-106000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-111000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-109000</v>
       </c>
       <c r="AG96" s="3">
         <v>-109000</v>
       </c>
       <c r="AH96" s="3">
-        <v>-90000</v>
+        <v>-109000</v>
       </c>
       <c r="AI96" s="3">
         <v>-90000</v>
@@ -10323,25 +10557,28 @@
         <v>-90000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-83000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-86000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-334000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-83000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-634000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-663000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-540000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-544000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-543000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-608000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-547000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-520000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-480000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-529000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-454000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-489000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-459000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-545000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-457000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-480000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1187000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-586000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-618000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-30000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-667000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-266000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-199000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-252000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-248000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-427000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-428000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>224000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-950000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-677000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-321000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-658000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-436000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>436000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-835000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6000</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>42000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>8000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>60000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>43000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-29000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-47000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>71000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-112000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>133000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>59000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-63000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>42000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-31000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-60000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>89000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>28000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>41000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-102000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>71000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>179000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>19000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-45000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-81000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>48000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>86000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-7000</v>
       </c>
-      <c r="AM102" s="3">
-        <v>0</v>
-      </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
         <v>-227000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>434000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>349000</v>
       </c>
     </row>
